--- a/data/trans_dic/P04D$notiene-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,91</t>
+          <t>2,78; 5,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,57; 21,71</t>
+          <t>15,39; 21,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,49</t>
+          <t>2,32; 5,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,22</t>
+          <t>3,12; 6,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 20,15</t>
+          <t>14,38; 20,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,63</t>
+          <t>3,52; 6,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,37</t>
+          <t>3,17; 5,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,85; 19,95</t>
+          <t>15,69; 19,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,43</t>
+          <t>3,43; 5,55</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,34</t>
+          <t>1,88; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 17,14</t>
+          <t>12,56; 17,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,46</t>
+          <t>3,78; 10,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,42</t>
+          <t>2,12; 4,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,24</t>
+          <t>11,69; 16,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 10,4</t>
+          <t>6,99; 10,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,98</t>
+          <t>2,23; 3,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,68; 15,96</t>
+          <t>12,77; 15,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,81</t>
+          <t>5,18; 9,82</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,64</t>
+          <t>5,76; 10,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 23,48</t>
+          <t>17,72; 23,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,96; 24,46</t>
+          <t>17,26; 24,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,34</t>
+          <t>3,99; 7,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 22,43</t>
+          <t>16,87; 22,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 21,92</t>
+          <t>8,63; 22,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,76</t>
+          <t>5,19; 7,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 22,08</t>
+          <t>17,92; 22,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,68; 21,42</t>
+          <t>11,37; 21,54</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,3</t>
+          <t>1,88; 4,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,85</t>
+          <t>8,77; 13,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 13,72</t>
+          <t>8,86; 13,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,92</t>
+          <t>3,99; 6,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,89</t>
+          <t>7,97; 11,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 35,67</t>
+          <t>9,6; 32,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,09</t>
+          <t>3,25; 5,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 11,73</t>
+          <t>9,0; 11,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 24,23</t>
+          <t>9,99; 23,47</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 4,89</t>
+          <t>3,43; 4,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,1</t>
+          <t>14,5; 17,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 11,96</t>
+          <t>8,32; 11,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,19</t>
+          <t>3,82; 5,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,83</t>
+          <t>13,45; 15,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 17,32</t>
+          <t>9,68; 17,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,84</t>
+          <t>3,83; 4,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,18; 15,97</t>
+          <t>14,21; 16,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,13</t>
+          <t>9,82; 14,18</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19408; 41394</t>
+          <t>19502; 39266</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>105063; 146474</t>
+          <t>103879; 145631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15568; 34777</t>
+          <t>14699; 34157</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21760; 43266</t>
+          <t>21679; 44116</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95955; 135577</t>
+          <t>96742; 134848</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26492; 48077</t>
+          <t>25533; 47854</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45152; 75035</t>
+          <t>44250; 76089</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>213544; 268875</t>
+          <t>211457; 267855</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45863; 73702</t>
+          <t>46522; 75430</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20664; 44052</t>
+          <t>19094; 43697</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128888; 175257</t>
+          <t>128412; 176575</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43892; 124722</t>
+          <t>45042; 127443</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22168; 45505</t>
+          <t>21883; 44892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>122204; 169400</t>
+          <t>121947; 167439</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68141; 99484</t>
+          <t>66805; 98985</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46918; 81315</t>
+          <t>45589; 80556</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>261868; 329682</t>
+          <t>263652; 329692</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118814; 210789</t>
+          <t>111307; 211017</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41446; 72922</t>
+          <t>43592; 76551</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>131828; 178358</t>
+          <t>134562; 181188</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119308; 172083</t>
+          <t>121475; 169754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29476; 56993</t>
+          <t>30984; 57706</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>130625; 176093</t>
+          <t>132408; 179656</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78875; 204132</t>
+          <t>80388; 205487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77655; 118928</t>
+          <t>79567; 120776</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>277090; 341021</t>
+          <t>276711; 347597</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>191012; 350306</t>
+          <t>185888; 352260</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18145; 40758</t>
+          <t>17832; 38694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81708; 120507</t>
+          <t>82254; 122508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84097; 126842</t>
+          <t>81936; 127160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42926; 72774</t>
+          <t>42017; 71555</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83706; 124148</t>
+          <t>83193; 123730</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>104645; 389518</t>
+          <t>104853; 358729</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65405; 101686</t>
+          <t>64998; 100089</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>176593; 232479</t>
+          <t>178325; 235450</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>204960; 488650</t>
+          <t>201445; 473298</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>117068; 167283</t>
+          <t>117374; 166824</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>488903; 580562</t>
+          <t>492038; 577072</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>276342; 413108</t>
+          <t>287278; 412953</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133591; 184342</t>
+          <t>135924; 184531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>473334; 561205</t>
+          <t>476803; 562513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>363645; 641776</t>
+          <t>358684; 652698</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>269870; 337742</t>
+          <t>266958; 339684</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>984256; 1108322</t>
+          <t>986040; 1118529</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>703057; 1011512</t>
+          <t>703072; 1014943</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$notiene-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,6</t>
+          <t>2,88; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 21,58</t>
+          <t>15,45; 21,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,39</t>
+          <t>3,37; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,34</t>
+          <t>2,93; 6,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,38; 20,04</t>
+          <t>14,1; 19,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,6</t>
+          <t>4,43; 7,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,45</t>
+          <t>3,24; 5,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 19,88</t>
+          <t>15,93; 19,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,55</t>
+          <t>4,29; 6,51</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,31</t>
+          <t>1,97; 4,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 17,27</t>
+          <t>12,58; 17,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 10,69</t>
+          <t>8,44; 12,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,36</t>
+          <t>2,14; 4,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 16,05</t>
+          <t>11,74; 16,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,35</t>
+          <t>7,61; 10,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,94</t>
+          <t>2,33; 3,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 15,96</t>
+          <t>12,7; 15,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,82</t>
+          <t>8,49; 11,5</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,12</t>
+          <t>5,56; 9,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 23,85</t>
+          <t>17,51; 23,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,26; 24,12</t>
+          <t>18,85; 25,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,43</t>
+          <t>3,92; 7,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,87; 22,89</t>
+          <t>16,6; 22,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 22,06</t>
+          <t>21,21; 26,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 7,88</t>
+          <t>5,03; 7,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,92; 22,5</t>
+          <t>17,91; 22,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 21,54</t>
+          <t>20,72; 25,13</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,08</t>
+          <t>1,81; 4,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,07</t>
+          <t>8,63; 12,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,75</t>
+          <t>9,62; 14,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,8</t>
+          <t>3,93; 6,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,85</t>
+          <t>8,14; 12,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 32,85</t>
+          <t>9,46; 12,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,01</t>
+          <t>3,25; 5,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 11,88</t>
+          <t>8,81; 11,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 23,47</t>
+          <t>10,04; 12,93</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,88</t>
+          <t>3,54; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 17,0</t>
+          <t>14,48; 17,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,32; 11,96</t>
+          <t>11,08; 13,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,19</t>
+          <t>3,81; 5,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 15,87</t>
+          <t>13,33; 15,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 17,62</t>
+          <t>11,33; 13,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 4,87</t>
+          <t>3,85; 4,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,21; 16,12</t>
+          <t>14,35; 15,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,18</t>
+          <t>11,51; 13,09</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>74754</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19502; 39266</t>
+          <t>20199; 41598</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>103879; 145631</t>
+          <t>104231; 146816</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14699; 34157</t>
+          <t>23209; 46615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21679; 44116</t>
+          <t>20389; 42095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96742; 134848</t>
+          <t>94893; 134159</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25533; 47854</t>
+          <t>32488; 54255</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44250; 76089</t>
+          <t>45202; 76421</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>211457; 267855</t>
+          <t>214654; 268621</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46522; 75430</t>
+          <t>60961; 92573</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>108914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82772</t>
+          <t>97262</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>173280</t>
+          <t>206177</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19094; 43697</t>
+          <t>19963; 45261</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128412; 176575</t>
+          <t>128652; 176391</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45042; 127443</t>
+          <t>88469; 134978</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21883; 44892</t>
+          <t>22037; 46541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121947; 167439</t>
+          <t>122457; 167179</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66805; 98985</t>
+          <t>81231; 115633</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45589; 80556</t>
+          <t>47620; 80094</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>263652; 329692</t>
+          <t>262222; 327453</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>111307; 211017</t>
+          <t>179720; 243251</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143943</t>
+          <t>175492</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>152583</t>
+          <t>194190</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>296526</t>
+          <t>369683</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43592; 76551</t>
+          <t>42092; 73918</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134562; 181188</t>
+          <t>132994; 179289</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>121475; 169754</t>
+          <t>150347; 206229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30984; 57706</t>
+          <t>30428; 59162</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>132408; 179656</t>
+          <t>130280; 175549</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80388; 205487</t>
+          <t>171806; 216599</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79567; 120776</t>
+          <t>77079; 120891</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>276711; 347597</t>
+          <t>276585; 342044</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185888; 352260</t>
+          <t>333201; 404018</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103861</t>
+          <t>117561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>172658</t>
+          <t>122233</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>276519</t>
+          <t>239793</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17832; 38694</t>
+          <t>17162; 38723</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82254; 122508</t>
+          <t>80896; 121613</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81936; 127160</t>
+          <t>95084; 141320</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42017; 71555</t>
+          <t>41357; 71686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83193; 123730</t>
+          <t>84924; 125338</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>104853; 358729</t>
+          <t>105536; 144404</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64998; 100089</t>
+          <t>64942; 102932</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>178325; 235450</t>
+          <t>174553; 234654</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>201445; 473298</t>
+          <t>211141; 271961</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>117374; 166824</t>
+          <t>121144; 170593</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>492038; 577072</t>
+          <t>491481; 577793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>287278; 412953</t>
+          <t>390405; 476922</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135924; 184531</t>
+          <t>135416; 186417</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>476803; 562513</t>
+          <t>472346; 560787</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>358684; 652698</t>
+          <t>422255; 496250</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>266958; 339684</t>
+          <t>268301; 339356</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>986040; 1118529</t>
+          <t>995617; 1107542</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>703072; 1014943</t>
+          <t>834312; 949008</t>
         </is>
       </c>
     </row>
